--- a/research/traditional_assets/database/data/switzerland/switzerland_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08044999999999999</v>
+        <v>0.0406</v>
       </c>
       <c r="E2">
-        <v>0.155</v>
+        <v>0.14</v>
       </c>
       <c r="F2">
-        <v>0.141</v>
+        <v>0.07825</v>
       </c>
       <c r="G2">
-        <v>0.1126301495817281</v>
+        <v>0.2734956278116342</v>
       </c>
       <c r="H2">
-        <v>0.1109866135178566</v>
+        <v>0.273155290773851</v>
       </c>
       <c r="I2">
-        <v>0.1466510972870047</v>
+        <v>0.2418707283487296</v>
       </c>
       <c r="J2">
-        <v>0.1332131132510455</v>
+        <v>0.2307689322074737</v>
       </c>
       <c r="K2">
-        <v>2992.211</v>
+        <v>2224.867</v>
       </c>
       <c r="L2">
-        <v>0.289725856557858</v>
+        <v>0.3008361717289041</v>
       </c>
       <c r="M2">
-        <v>2204.54569</v>
+        <v>2752.52212</v>
       </c>
       <c r="N2">
-        <v>0.03069068537165656</v>
+        <v>0.06954765005369212</v>
       </c>
       <c r="O2">
-        <v>0.7367614416229337</v>
+        <v>1.237162544997072</v>
       </c>
       <c r="P2">
-        <v>1770.61569</v>
+        <v>1568.01412</v>
       </c>
       <c r="Q2">
-        <v>0.02464970869163914</v>
+        <v>0.03961882685869497</v>
       </c>
       <c r="R2">
-        <v>0.5917415884107105</v>
+        <v>0.7047675748707675</v>
       </c>
       <c r="S2">
-        <v>433.9300000000001</v>
+        <v>1184.508</v>
       </c>
       <c r="T2">
-        <v>0.1968342057814189</v>
+        <v>0.4303355062592558</v>
       </c>
       <c r="U2">
-        <v>48177.254</v>
+        <v>31121.202</v>
       </c>
       <c r="V2">
-        <v>0.6707018826107354</v>
+        <v>0.786335721053629</v>
       </c>
       <c r="W2">
-        <v>0.1499409681227863</v>
+        <v>0.07931848016881786</v>
       </c>
       <c r="X2">
-        <v>0.0454091259771644</v>
+        <v>0.07387315407617154</v>
       </c>
       <c r="Y2">
-        <v>0.1045318421456219</v>
+        <v>0.005445326092646322</v>
       </c>
       <c r="Z2">
-        <v>1.102788956725403</v>
+        <v>0.5837040225926845</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.002432748538011695</v>
       </c>
       <c r="AB2">
-        <v>0.04395973371960109</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC2">
-        <v>-0.04408243032082342</v>
+        <v>-0.06830843328424305</v>
       </c>
       <c r="AD2">
-        <v>44761.72</v>
+        <v>27509.62</v>
       </c>
       <c r="AE2">
-        <v>0.2638485694419172</v>
+        <v>0.1971135842615913</v>
       </c>
       <c r="AF2">
-        <v>44761.98384856944</v>
+        <v>27509.81711358426</v>
       </c>
       <c r="AG2">
-        <v>-3415.270151430559</v>
+        <v>-3611.384886415737</v>
       </c>
       <c r="AH2">
-        <v>0.3839162870647293</v>
+        <v>0.4100598786355984</v>
       </c>
       <c r="AI2">
-        <v>0.7251717598876514</v>
+        <v>0.7303138305138751</v>
       </c>
       <c r="AJ2">
-        <v>-0.04991929731744636</v>
+        <v>-0.1004107581541864</v>
       </c>
       <c r="AK2">
-        <v>-0.2520719702351249</v>
+        <v>-0.551585095770896</v>
       </c>
       <c r="AL2">
-        <v>19.768</v>
+        <v>17.56</v>
       </c>
       <c r="AM2">
-        <v>16.265</v>
+        <v>12.427</v>
       </c>
       <c r="AN2">
-        <v>30.57709661267152</v>
+        <v>15.41843613086627</v>
       </c>
       <c r="AO2">
-        <v>76.61736139214892</v>
+        <v>101.8660592255125</v>
       </c>
       <c r="AP2">
-        <v>-2.332998941476456</v>
+        <v>-2.024088563025472</v>
       </c>
       <c r="AQ2">
-        <v>93.11847525361205</v>
+        <v>143.9420616399775</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Partners Group Holding AG (SWX:PGHN)</t>
+          <t>VZ Holding AG (SWX:VZN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.195</v>
+        <v>0.103</v>
       </c>
       <c r="E3">
-        <v>0.208</v>
-      </c>
-      <c r="F3">
-        <v>0.176</v>
+        <v>0.115</v>
       </c>
       <c r="G3">
-        <v>0.4885787414883856</v>
+        <v>0.4455813953488372</v>
       </c>
       <c r="H3">
-        <v>0.4885787414883856</v>
+        <v>0.4455813953488372</v>
       </c>
       <c r="I3">
-        <v>0.6225431013666876</v>
+        <v>0.4316279069767442</v>
       </c>
       <c r="J3">
-        <v>0.5309063680408224</v>
+        <v>0.3711673186008779</v>
       </c>
       <c r="K3">
-        <v>1212.6</v>
+        <v>158.4</v>
       </c>
       <c r="L3">
-        <v>0.5855990727773217</v>
+        <v>0.3683720930232559</v>
       </c>
       <c r="M3">
-        <v>959.5</v>
+        <v>78.8</v>
       </c>
       <c r="N3">
-        <v>0.02203386716758599</v>
+        <v>0.0258022265880812</v>
       </c>
       <c r="O3">
-        <v>0.7912749463961736</v>
+        <v>0.4974747474747475</v>
       </c>
       <c r="P3">
-        <v>783.8</v>
+        <v>64.8</v>
       </c>
       <c r="Q3">
-        <v>0.01799910900047305</v>
+        <v>0.0212180746561886</v>
       </c>
       <c r="R3">
-        <v>0.6463796800263896</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="S3">
-        <v>175.7</v>
+        <v>14</v>
       </c>
       <c r="T3">
-        <v>0.1831162063574779</v>
+        <v>0.1776649746192893</v>
       </c>
       <c r="U3">
-        <v>467.8</v>
+        <v>1770.3</v>
       </c>
       <c r="V3">
-        <v>0.01074251491505651</v>
+        <v>0.5796660117878193</v>
       </c>
       <c r="W3">
-        <v>0.6631302635896313</v>
+        <v>0.2349799732977303</v>
       </c>
       <c r="X3">
-        <v>0.04439722655163834</v>
+        <v>0.07997411874281787</v>
       </c>
       <c r="Y3">
-        <v>0.618733037037993</v>
-      </c>
-      <c r="Z3">
-        <v>1.106320457338249</v>
-      </c>
-      <c r="AA3">
-        <v>0.5873525758947112</v>
+        <v>0.1550058545549124</v>
       </c>
       <c r="AB3">
-        <v>0.04388270925153568</v>
-      </c>
-      <c r="AC3">
-        <v>0.5434698666431755</v>
+        <v>0.07115399820919299</v>
       </c>
       <c r="AD3">
-        <v>932.7</v>
+        <v>832.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>932.7</v>
+        <v>832.2</v>
       </c>
       <c r="AG3">
-        <v>464.9</v>
+        <v>-938.0999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.02096930482269281</v>
+        <v>0.2141423498533272</v>
       </c>
       <c r="AI3">
-        <v>0.2807815040038533</v>
+        <v>0.5349016583108368</v>
       </c>
       <c r="AJ3">
-        <v>0.0105631482680663</v>
+        <v>-0.4433574365518219</v>
       </c>
       <c r="AK3">
-        <v>0.1628941836019622</v>
+        <v>4.373426573426575</v>
       </c>
       <c r="AL3">
-        <v>8.98</v>
+        <v>0.674</v>
       </c>
       <c r="AM3">
-        <v>6.17</v>
+        <v>0.65</v>
       </c>
       <c r="AN3">
-        <v>0.7175719341437145</v>
+        <v>4.289690721649484</v>
       </c>
       <c r="AO3">
-        <v>143.5523385300668</v>
+        <v>275.3709198813056</v>
       </c>
       <c r="AP3">
-        <v>0.3576704108324358</v>
+        <v>-4.835567010309278</v>
       </c>
       <c r="AQ3">
-        <v>208.9303079416532</v>
+        <v>285.5384615384615</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spice Private Equity AG (SWX:SPCE)</t>
+          <t>Partners Group Holding AG (SWX:PGHN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,106 +850,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.227</v>
+        <v>0.169</v>
       </c>
       <c r="E4">
-        <v>0.414</v>
+        <v>0.144</v>
+      </c>
+      <c r="F4">
+        <v>0.0603</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.737037335698734</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.737037335698734</v>
       </c>
       <c r="I4">
-        <v>0.9035369774919614</v>
+        <v>0.6436980888638013</v>
       </c>
       <c r="J4">
-        <v>0.9035369774919614</v>
+        <v>0.5487434400583017</v>
       </c>
       <c r="K4">
-        <v>27.9</v>
+        <v>1359.8</v>
       </c>
       <c r="L4">
-        <v>0.8971061093247588</v>
+        <v>0.5482622369163778</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1551.9</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.06736554238833181</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.141270775113987</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>901.7</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.03914138125623996</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.663112222385645</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>650.2</v>
+      </c>
+      <c r="T4">
+        <v>0.418970294477737</v>
       </c>
       <c r="U4">
-        <v>67.3</v>
+        <v>321.8</v>
       </c>
       <c r="V4">
-        <v>0.8031026252983293</v>
+        <v>0.01396883274731953</v>
       </c>
       <c r="W4">
-        <v>0.2233787029623699</v>
+        <v>0.569168306056674</v>
       </c>
       <c r="X4">
-        <v>0.04387296409148227</v>
+        <v>0.07387315407617154</v>
       </c>
       <c r="Y4">
-        <v>0.1795057388708876</v>
+        <v>0.4952951519805024</v>
       </c>
       <c r="Z4">
-        <v>0.3154158215010142</v>
+        <v>0.8690259285213734</v>
       </c>
       <c r="AA4">
-        <v>0.2849898580121704</v>
+        <v>0.4768722775166783</v>
       </c>
       <c r="AB4">
-        <v>0.04387296409148227</v>
+        <v>0.07215729279577085</v>
       </c>
       <c r="AC4">
-        <v>0.2411168939206881</v>
+        <v>0.4047149847209074</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1184.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1184.5</v>
       </c>
       <c r="AG4">
-        <v>-67.3</v>
+        <v>862.7</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.04890283425881965</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.3522990898816252</v>
       </c>
       <c r="AJ4">
-        <v>-4.078787878787878</v>
+        <v>0.03609668740611807</v>
       </c>
       <c r="AK4">
-        <v>-0.7871345029239765</v>
+        <v>0.2837455597947639</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>8.17</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>4.82</v>
+      </c>
+      <c r="AN4">
+        <v>0.7364919480196481</v>
+      </c>
+      <c r="AO4">
+        <v>195.4100367197063</v>
+      </c>
+      <c r="AP4">
+        <v>0.5364048995834111</v>
+      </c>
+      <c r="AQ4">
+        <v>331.2240663900415</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alpine Select AG (SWX:ALPN)</t>
+          <t>AP Alternative Portfolio AG (BRSE:APN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,7 +987,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>1.455</v>
+        <v>0.147</v>
+      </c>
+      <c r="E5">
+        <v>0.14</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,109 +999,97 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.9231133220743082</v>
+        <v>0.904040404040404</v>
       </c>
       <c r="J5">
-        <v>0.8708728253910033</v>
+        <v>0.904040404040404</v>
       </c>
       <c r="K5">
-        <v>27.4</v>
+        <v>14.2</v>
       </c>
       <c r="L5">
-        <v>0.8106508875739645</v>
+        <v>0.7171717171717171</v>
       </c>
       <c r="M5">
-        <v>14.64</v>
+        <v>21.54</v>
       </c>
       <c r="N5">
-        <v>0.09760000000000001</v>
+        <v>0.4929061784897025</v>
       </c>
       <c r="O5">
-        <v>0.5343065693430658</v>
+        <v>1.516901408450704</v>
       </c>
       <c r="P5">
-        <v>9.66</v>
+        <v>2.84</v>
       </c>
       <c r="Q5">
-        <v>0.0644</v>
+        <v>0.06498855835240273</v>
       </c>
       <c r="R5">
-        <v>0.3525547445255475</v>
+        <v>0.2</v>
       </c>
       <c r="S5">
-        <v>4.98</v>
+        <v>18.7</v>
       </c>
       <c r="T5">
-        <v>0.3401639344262295</v>
+        <v>0.8681522748375116</v>
       </c>
       <c r="U5">
-        <v>8.699999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="V5">
-        <v>0.058</v>
+        <v>0.06887871853546911</v>
       </c>
       <c r="W5">
-        <v>0.2238562091503268</v>
+        <v>0.1865965834428384</v>
       </c>
       <c r="X5">
-        <v>0.0454091259771644</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y5">
-        <v>0.1784470831731624</v>
+        <v>0.1141423644021335</v>
       </c>
       <c r="Z5">
-        <v>0.3119121408680887</v>
+        <v>0.3</v>
       </c>
       <c r="AA5">
-        <v>0.271635807391549</v>
+        <v>0.2712121212121212</v>
       </c>
       <c r="AB5">
-        <v>0.04390040800895952</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC5">
-        <v>0.2277353993825895</v>
+        <v>0.1987579021714163</v>
       </c>
       <c r="AD5">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.2638485694419172</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>9.413848569441917</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>0.7138485694419181</v>
+        <v>-3.01</v>
       </c>
       <c r="AH5">
-        <v>0.05905289066113457</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.06068992972750266</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.004736449743787213</v>
+        <v>-0.07397394937331038</v>
       </c>
       <c r="AK5">
-        <v>0.004875553620212028</v>
+        <v>-0.05226601840597325</v>
       </c>
       <c r="AL5">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.09</v>
-      </c>
-      <c r="AN5">
-        <v>169.4444444444445</v>
-      </c>
-      <c r="AO5">
-        <v>346.6666666666667</v>
-      </c>
-      <c r="AP5">
-        <v>13.21941795262811</v>
-      </c>
-      <c r="AQ5">
-        <v>346.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AP Alternative Portfolio AG (BRSE:APN)</t>
+          <t>Matador Partners Group AG (BRSE:SQL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1111,110 +1108,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0732</v>
-      </c>
-      <c r="E6">
-        <v>0.142</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.6104651162790697</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.6104651162790697</v>
       </c>
       <c r="I6">
-        <v>0.8608247422680413</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="J6">
-        <v>0.8608247422680413</v>
+        <v>0.7719324887191947</v>
       </c>
       <c r="K6">
-        <v>20.2</v>
+        <v>12.2</v>
       </c>
       <c r="L6">
-        <v>1.041237113402062</v>
+        <v>0.7093023255813954</v>
       </c>
       <c r="M6">
-        <v>16.8849</v>
+        <v>7.06</v>
       </c>
       <c r="N6">
-        <v>0.2581788990825688</v>
+        <v>0.108282208588957</v>
       </c>
       <c r="O6">
-        <v>0.8358861386138615</v>
+        <v>0.578688524590164</v>
       </c>
       <c r="P6">
-        <v>3.084900000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.04716972477064221</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1527178217821782</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>13.8</v>
+        <v>7.06</v>
       </c>
       <c r="T6">
-        <v>0.8172982961107261</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>10.1</v>
+        <v>1.18</v>
       </c>
       <c r="V6">
-        <v>0.154434250764526</v>
+        <v>0.01809815950920245</v>
       </c>
       <c r="W6">
-        <v>0.2953216374269005</v>
+        <v>0.2505133470225873</v>
       </c>
       <c r="X6">
-        <v>0.04387296409148227</v>
+        <v>0.08261242503335933</v>
       </c>
       <c r="Y6">
-        <v>0.2514486733354183</v>
+        <v>0.1679009219892279</v>
       </c>
       <c r="Z6">
-        <v>0.3009151543353498</v>
+        <v>0.2527924750146972</v>
       </c>
       <c r="AA6">
-        <v>0.2590352101752753</v>
+        <v>0.1951387243675801</v>
       </c>
       <c r="AB6">
-        <v>0.04387296409148227</v>
+        <v>0.07082056179568418</v>
       </c>
       <c r="AC6">
-        <v>0.215162246083793</v>
+        <v>0.1243181625718959</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG6">
-        <v>-10.1</v>
+        <v>22.82</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.2690582959641256</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.2891566265060241</v>
       </c>
       <c r="AJ6">
-        <v>-0.1826401446654611</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="AK6">
-        <v>-0.153030303030303</v>
+        <v>0.2789049132241506</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="AN6">
+        <v>1.655172413793103</v>
+      </c>
+      <c r="AO6">
+        <v>15.50802139037433</v>
+      </c>
+      <c r="AP6">
+        <v>1.573793103448276</v>
+      </c>
+      <c r="AQ6">
+        <v>15.50802139037433</v>
       </c>
     </row>
     <row r="7">
@@ -1225,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Varia Europe Properties AG (BRSE:VARE)</t>
+          <t>Alpine Select AG (SWX:ALPN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1233,6 +1236,9 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.247</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1240,97 +1246,109 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.5944444444444444</v>
+        <v>0.8798829605385354</v>
       </c>
       <c r="J7">
-        <v>0.4090036231884058</v>
+        <v>0.8798829605385354</v>
       </c>
       <c r="K7">
-        <v>0.633</v>
+        <v>-13.4</v>
       </c>
       <c r="L7">
-        <v>0.3516666666666667</v>
+        <v>-0.6473429951690821</v>
       </c>
       <c r="M7">
-        <v>1.5675</v>
+        <v>9.907999999999999</v>
       </c>
       <c r="N7">
-        <v>0.02839673913043478</v>
+        <v>0.08548748921484037</v>
       </c>
       <c r="O7">
-        <v>2.476303317535545</v>
+        <v>-0.7394029850746268</v>
       </c>
       <c r="P7">
-        <v>1.5675</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.02839673913043478</v>
+        <v>0.0800690250215703</v>
       </c>
       <c r="R7">
-        <v>2.476303317535545</v>
+        <v>-0.6925373134328358</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.6280000000000001</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.06338312474767865</v>
       </c>
       <c r="U7">
-        <v>0.509</v>
+        <v>2.94</v>
       </c>
       <c r="V7">
-        <v>0.009221014492753622</v>
+        <v>0.02536669542709232</v>
       </c>
       <c r="W7">
-        <v>0.0131055900621118</v>
+        <v>-0.09745454545454546</v>
       </c>
       <c r="X7">
-        <v>0.04387296409148227</v>
+        <v>0.07642989825285378</v>
       </c>
       <c r="Y7">
-        <v>-0.03076737402937047</v>
+        <v>-0.1738844437073992</v>
       </c>
       <c r="Z7">
-        <v>0.03828158230540196</v>
+        <v>0.1498402642149611</v>
       </c>
       <c r="AA7">
-        <v>0.01565730586429457</v>
+        <v>0.1318418952853363</v>
       </c>
       <c r="AB7">
-        <v>0.04387296409148227</v>
+        <v>0.07168964088305164</v>
       </c>
       <c r="AC7">
-        <v>-0.02821565822718771</v>
+        <v>0.06015225440228468</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>0.1971135842615913</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>16.69711358426159</v>
       </c>
       <c r="AG7">
-        <v>-0.509</v>
+        <v>13.75711358426159</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.1259236580112361</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.1223257631301795</v>
       </c>
       <c r="AJ7">
-        <v>-0.009306832934120787</v>
+        <v>0.1061038087611068</v>
       </c>
       <c r="AK7">
-        <v>-0.009982153713400404</v>
+        <v>0.1030054724534173</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.119</v>
+      </c>
+      <c r="AN7">
+        <v>311.3207547169811</v>
+      </c>
+      <c r="AO7">
+        <v>152.9411764705882</v>
+      </c>
+      <c r="AP7">
+        <v>259.5681808351243</v>
+      </c>
+      <c r="AQ7">
+        <v>152.9411764705882</v>
       </c>
     </row>
     <row r="8">
@@ -1350,10 +1368,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.152</v>
-      </c>
-      <c r="E8">
-        <v>0.41</v>
+        <v>0.00728</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1362,67 +1377,67 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.5239263803680981</v>
+        <v>0.68359375</v>
       </c>
       <c r="J8">
-        <v>0.4779414750408262</v>
+        <v>0.68359375</v>
       </c>
       <c r="K8">
-        <v>12.7</v>
+        <v>-2.36</v>
       </c>
       <c r="L8">
-        <v>7.791411042944786</v>
+        <v>-0.9218749999999999</v>
       </c>
       <c r="M8">
-        <v>10.98329</v>
+        <v>9.784120000000001</v>
       </c>
       <c r="N8">
-        <v>0.1221723025583982</v>
+        <v>0.117315587529976</v>
       </c>
       <c r="O8">
-        <v>0.8648259842519685</v>
+        <v>-4.145813559322034</v>
       </c>
       <c r="P8">
-        <v>3.95329</v>
+        <v>4.784120000000001</v>
       </c>
       <c r="Q8">
-        <v>0.04397430478309233</v>
+        <v>0.05736354916067147</v>
       </c>
       <c r="R8">
-        <v>0.3112826771653544</v>
+        <v>-2.027169491525424</v>
       </c>
       <c r="S8">
-        <v>7.029999999999999</v>
+        <v>5.000000000000001</v>
       </c>
       <c r="T8">
-        <v>0.6400632233146898</v>
+        <v>0.5110321623201678</v>
       </c>
       <c r="U8">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>0.1479421579532814</v>
+        <v>0.1199040767386091</v>
       </c>
       <c r="W8">
-        <v>0.1499409681227863</v>
+        <v>-0.02471204188481675</v>
       </c>
       <c r="X8">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y8">
-        <v>0.106068004031304</v>
+        <v>-0.09716626092552161</v>
       </c>
       <c r="Z8">
-        <v>0.02418397626112759</v>
+        <v>0.03114355231143552</v>
       </c>
       <c r="AA8">
-        <v>0.01155852528659565</v>
+        <v>0.02128953771289538</v>
       </c>
       <c r="AB8">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC8">
-        <v>-0.03231443880488662</v>
+        <v>-0.05116468132780948</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1434,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-13.3</v>
+        <v>-10</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1443,19 +1458,22 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.1736292428198433</v>
+        <v>-0.1362397820163488</v>
       </c>
       <c r="AK8">
-        <v>-0.1618004866180049</v>
+        <v>-0.1328021248339973</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AM8">
-        <v>-0.571</v>
+        <v>0.138</v>
+      </c>
+      <c r="AO8">
+        <v>12.68115942028985</v>
       </c>
       <c r="AQ8">
-        <v>-1.495621716287215</v>
+        <v>12.68115942028985</v>
       </c>
     </row>
     <row r="9">
@@ -1466,7 +1484,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bellevue Group AG (SWX:BBN)</t>
+          <t>Varia Europe Properties AG (BRSE:VARE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1474,104 +1492,98 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.138</v>
-      </c>
-      <c r="E9">
-        <v>0.168</v>
-      </c>
       <c r="G9">
-        <v>0.01546885694729637</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.6358024691358024</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.6358024691358024</v>
       </c>
       <c r="K9">
-        <v>42.5</v>
+        <v>1.29</v>
       </c>
       <c r="L9">
-        <v>0.2908966461327858</v>
+        <v>0.7962962962962963</v>
       </c>
       <c r="M9">
-        <v>34</v>
+        <v>1.47</v>
       </c>
       <c r="N9">
-        <v>0.05640345056403451</v>
+        <v>0.04375</v>
       </c>
       <c r="O9">
-        <v>0.8</v>
+        <v>1.13953488372093</v>
       </c>
       <c r="P9">
-        <v>20.9</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
-        <v>0.03467153284671533</v>
+        <v>0.04375</v>
       </c>
       <c r="R9">
-        <v>0.4917647058823529</v>
+        <v>1.13953488372093</v>
       </c>
       <c r="S9">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.3852941176470588</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>57.5</v>
+        <v>0.542</v>
       </c>
       <c r="V9">
-        <v>0.09538818845388189</v>
+        <v>0.01613095238095238</v>
       </c>
       <c r="W9">
-        <v>0.272785622593068</v>
+        <v>0.02504854368932039</v>
       </c>
       <c r="X9">
-        <v>0.04401752064683619</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y9">
-        <v>0.2287681019462318</v>
+        <v>-0.04740567535138447</v>
       </c>
       <c r="Z9">
-        <v>2.604278074866309</v>
+        <v>0.03177031240807202</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>0.02019964307426801</v>
       </c>
       <c r="AB9">
-        <v>0.04387569259424015</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC9">
-        <v>-0.04387569259424015</v>
+        <v>-0.05225457596643684</v>
       </c>
       <c r="AD9">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>-53.94</v>
+        <v>-0.542</v>
       </c>
       <c r="AH9">
-        <v>0.005871099676759682</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.02455849889624724</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.09827642750428162</v>
+        <v>-0.01639542622058201</v>
       </c>
       <c r="AK9">
-        <v>-0.616739080722616</v>
+        <v>-0.01213668323704599</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vontobel Holding AG (SWX:VONN)</t>
+          <t>Julius Bär Gruppe AG (SWX:BAER)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,10 +1609,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0794</v>
+        <v>0.0432</v>
       </c>
       <c r="E10">
-        <v>0.106</v>
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F10">
+        <v>0.09619999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1615,85 +1630,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>327.6</v>
+        <v>970.6</v>
       </c>
       <c r="L10">
-        <v>0.2129900526623757</v>
+        <v>0.248489503328213</v>
       </c>
       <c r="M10">
-        <v>210.3</v>
+        <v>1043.8</v>
       </c>
       <c r="N10">
-        <v>0.0428763660088077</v>
+        <v>0.08879701230976018</v>
       </c>
       <c r="O10">
-        <v>0.6419413919413919</v>
+        <v>1.075417267669483</v>
       </c>
       <c r="P10">
-        <v>137.5</v>
+        <v>580.3</v>
       </c>
       <c r="Q10">
-        <v>0.02803376284456043</v>
+        <v>0.04936664710035815</v>
       </c>
       <c r="R10">
-        <v>0.4197191697191697</v>
+        <v>0.5978776014836183</v>
       </c>
       <c r="S10">
-        <v>72.80000000000001</v>
+        <v>463.5</v>
       </c>
       <c r="T10">
-        <v>0.3461721350451736</v>
+        <v>0.4440505844031424</v>
       </c>
       <c r="U10">
-        <v>8767.5</v>
+        <v>28735.4</v>
       </c>
       <c r="V10">
-        <v>1.787534659924971</v>
+        <v>2.444546529532365</v>
       </c>
       <c r="W10">
-        <v>0.1767466954410575</v>
+        <v>0.1335884166483153</v>
       </c>
       <c r="X10">
-        <v>0.05949656679538454</v>
+        <v>0.1318574242478292</v>
       </c>
       <c r="Y10">
-        <v>0.1172501286456729</v>
+        <v>0.001730992400486131</v>
       </c>
       <c r="Z10">
-        <v>-0.5162448815197691</v>
+        <v>0.4432893751276754</v>
       </c>
       <c r="AA10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04405402866716262</v>
+        <v>0.06830843328424305</v>
       </c>
       <c r="AC10">
-        <v>-0.04405402866716262</v>
+        <v>-0.06830843328424305</v>
       </c>
       <c r="AD10">
-        <v>3130.7</v>
+        <v>25303.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>3130.7</v>
+        <v>25303.2</v>
       </c>
       <c r="AG10">
-        <v>-5636.8</v>
+        <v>-3432.200000000001</v>
       </c>
       <c r="AH10">
-        <v>0.3896086117852031</v>
+        <v>0.6827980927246675</v>
       </c>
       <c r="AI10">
-        <v>0.5963238095238095</v>
+        <v>0.7987474193935339</v>
       </c>
       <c r="AJ10">
-        <v>7.700546448087432</v>
+        <v>-0.4123902099078425</v>
       </c>
       <c r="AK10">
-        <v>1.602501776830135</v>
+        <v>-1.166145691764067</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1710,7 +1725,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EFG International AG (SWX:EFGN)</t>
+          <t>Spice Private Equity AG (SWX:SPCE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1719,10 +1734,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.118</v>
-      </c>
-      <c r="E11">
-        <v>0.429</v>
+        <v>-0.111</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1731,91 +1743,91 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.05430809399477807</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.05430809399477807</v>
       </c>
       <c r="K11">
-        <v>202.3</v>
+        <v>0.141</v>
       </c>
       <c r="L11">
-        <v>0.156542598467848</v>
+        <v>0.03681462140992166</v>
       </c>
       <c r="M11">
-        <v>144.2</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N11">
-        <v>0.06248104337276311</v>
+        <v>0.1113428943937418</v>
       </c>
       <c r="O11">
-        <v>0.7128027681660899</v>
+        <v>60.56737588652482</v>
       </c>
       <c r="P11">
-        <v>144.2</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.06248104337276311</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.7128027681660899</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>11986.9</v>
+        <v>45.5</v>
       </c>
       <c r="V11">
-        <v>5.193855886303566</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="W11">
-        <v>0.1165792658329972</v>
+        <v>0.0009227748691099474</v>
       </c>
       <c r="X11">
-        <v>0.0639582566321293</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y11">
-        <v>0.05262100920086789</v>
+        <v>-0.0715314441715949</v>
       </c>
       <c r="Z11">
-        <v>-0.1628812704814721</v>
+        <v>0.0447953216374269</v>
       </c>
       <c r="AA11">
-        <v>-0</v>
+        <v>0.002432748538011695</v>
       </c>
       <c r="AB11">
-        <v>0.04408243032082342</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC11">
-        <v>-0.04408243032082342</v>
+        <v>-0.07002147050269317</v>
       </c>
       <c r="AD11">
-        <v>1893.8</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1893.8</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>-10093.1</v>
+        <v>-45.5</v>
       </c>
       <c r="AH11">
-        <v>0.4507223266772973</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.4378728323699422</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1.296447104762883</v>
+        <v>-1.458333333333333</v>
       </c>
       <c r="AK11">
-        <v>1.317310327725499</v>
+        <v>-0.4600606673407482</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1832,7 +1844,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>One Swiss Bank SA (SWX:ONE)</t>
+          <t>Bellevue Group AG (SWX:BBN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1841,10 +1853,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0357</v>
+        <v>0.034</v>
+      </c>
+      <c r="E12">
+        <v>0.428</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.01753794266441821</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1856,85 +1871,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>-2.67</v>
+        <v>36.5</v>
       </c>
       <c r="L12">
-        <v>-0.1948905109489051</v>
+        <v>0.3077571669477235</v>
       </c>
       <c r="M12">
-        <v>9.390000000000001</v>
+        <v>13.44</v>
       </c>
       <c r="N12">
-        <v>0.1904665314401623</v>
+        <v>0.02497212931995541</v>
       </c>
       <c r="O12">
-        <v>-3.51685393258427</v>
+        <v>0.3682191780821918</v>
       </c>
       <c r="P12">
-        <v>9.390000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="Q12">
-        <v>0.1904665314401623</v>
+        <v>0.005276848755109624</v>
       </c>
       <c r="R12">
-        <v>-3.51685393258427</v>
+        <v>0.07780821917808219</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.7886904761904762</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>0.07209215904868077</v>
       </c>
       <c r="W12">
-        <v>-0.04564102564102564</v>
+        <v>0.2581329561527581</v>
       </c>
       <c r="X12">
-        <v>0.04518370859166335</v>
+        <v>0.0726039434221078</v>
       </c>
       <c r="Y12">
-        <v>-0.09082473423268898</v>
+        <v>0.1855290127306503</v>
       </c>
       <c r="Z12">
-        <v>0.2439675897070608</v>
+        <v>2.840038314176245</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04409625689006767</v>
+        <v>0.0724214545198448</v>
       </c>
       <c r="AC12">
-        <v>-0.04409625689006767</v>
+        <v>-0.0724214545198448</v>
       </c>
       <c r="AD12">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="AG12">
-        <v>2.64</v>
+        <v>-35.88</v>
       </c>
       <c r="AH12">
-        <v>0.05082787832113978</v>
+        <v>0.005396215257244234</v>
       </c>
       <c r="AI12">
-        <v>0.04122423485321675</v>
+        <v>0.02159443869250111</v>
       </c>
       <c r="AJ12">
-        <v>0.05082787832113978</v>
+        <v>-0.07142857142857141</v>
       </c>
       <c r="AK12">
-        <v>0.04122423485321675</v>
+        <v>-0.3721219663970129</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1951,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Julius Bär Gruppe AG (SWX:BAER)</t>
+          <t>One Swiss Bank SA (SWX:ONE)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1960,13 +1975,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.06559999999999999</v>
-      </c>
-      <c r="E13">
-        <v>0.129</v>
-      </c>
-      <c r="F13">
-        <v>0.106</v>
+        <v>0.215</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1981,85 +1990,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>879.2</v>
+        <v>-2.97</v>
       </c>
       <c r="L13">
-        <v>0.2181962575073212</v>
+        <v>-0.08761061946902655</v>
       </c>
       <c r="M13">
-        <v>707.3000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.05119760262321663</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.8044813466787989</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>596.7</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.04319186976569116</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.6786851683348499</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>110.6</v>
-      </c>
-      <c r="T13">
-        <v>0.1563692916725576</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>24582.1</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.779364608290928</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>0.1325853540837254</v>
+        <v>-0.04706814580031696</v>
       </c>
       <c r="X13">
-        <v>0.09016555721081576</v>
+        <v>0.09104674903446375</v>
       </c>
       <c r="Y13">
-        <v>0.04241979687290967</v>
+        <v>-0.1381148948347807</v>
       </c>
       <c r="Z13">
-        <v>0.6763121233991841</v>
+        <v>0.5295220243673852</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.04417696072084203</v>
+        <v>0.07380601714464163</v>
       </c>
       <c r="AC13">
-        <v>-0.04417696072084203</v>
+        <v>-0.07380601714464163</v>
       </c>
       <c r="AD13">
-        <v>26127.9</v>
+        <v>15.9</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>26127.9</v>
+        <v>15.9</v>
       </c>
       <c r="AG13">
-        <v>1545.800000000003</v>
+        <v>15.9</v>
       </c>
       <c r="AH13">
-        <v>0.6541296347294896</v>
+        <v>0.4025316455696203</v>
       </c>
       <c r="AI13">
-        <v>0.7822162479342801</v>
+        <v>0.2615131578947368</v>
       </c>
       <c r="AJ13">
-        <v>0.1006321244197933</v>
+        <v>0.4025316455696203</v>
       </c>
       <c r="AK13">
-        <v>0.1752548099271003</v>
+        <v>0.2615131578947368</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2076,7 +2082,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leonteq AG (SWX:LEON)</t>
+          <t>GAM Holding AG (SWX:GAM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2085,109 +2091,118 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0815</v>
-      </c>
-      <c r="E14">
-        <v>0.102</v>
+        <v>-0.172</v>
       </c>
       <c r="G14">
-        <v>0.03892215568862276</v>
+        <v>-0.01843796342066238</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>-0.01843796342066238</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-0.1576866040533861</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>-0.1576866040533861</v>
       </c>
       <c r="K14">
-        <v>117.7</v>
+        <v>-309.8</v>
       </c>
       <c r="L14">
-        <v>0.3203592814371258</v>
+        <v>-1.531389026198715</v>
       </c>
       <c r="M14">
-        <v>21.66</v>
+        <v>5.13</v>
       </c>
       <c r="N14">
-        <v>0.0155391348016357</v>
+        <v>0.03230478589420654</v>
       </c>
       <c r="O14">
-        <v>0.1840271877655055</v>
+        <v>-0.01655907036797934</v>
       </c>
       <c r="P14">
-        <v>7.46</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.005351890379510725</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.06338147833474936</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>14.2</v>
+        <v>5.13</v>
       </c>
       <c r="T14">
-        <v>0.6555863342566943</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>60.5</v>
+        <v>179.8</v>
       </c>
       <c r="V14">
-        <v>0.04340340053088457</v>
+        <v>1.132241813602015</v>
       </c>
       <c r="W14">
-        <v>0.1691578039666571</v>
+        <v>-0.5816748028539241</v>
       </c>
       <c r="X14">
-        <v>0.2462314224172394</v>
+        <v>0.08003108074815624</v>
       </c>
       <c r="Y14">
-        <v>-0.07707361845058228</v>
+        <v>-0.6617058836020804</v>
       </c>
       <c r="Z14">
-        <v>0.0310973803377206</v>
+        <v>0.601010101010101</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>-0.09477124183006534</v>
       </c>
       <c r="AB14">
-        <v>0.04428755049461136</v>
+        <v>0.07250640129845459</v>
       </c>
       <c r="AC14">
-        <v>-0.04428755049461136</v>
+        <v>-0.1672776431285199</v>
       </c>
       <c r="AD14">
-        <v>11523.7</v>
+        <v>43.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>11523.7</v>
+        <v>43.6</v>
       </c>
       <c r="AG14">
-        <v>11463.2</v>
+        <v>-136.2</v>
       </c>
       <c r="AH14">
-        <v>0.892092958444293</v>
+        <v>0.2154150197628459</v>
       </c>
       <c r="AI14">
-        <v>0.936581599479844</v>
+        <v>0.1694520015546055</v>
       </c>
       <c r="AJ14">
-        <v>0.8915851941728695</v>
+        <v>-6.026548672566374</v>
       </c>
       <c r="AK14">
-        <v>0.9362682239555683</v>
+        <v>-1.75741935483871</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>3.35</v>
+      </c>
+      <c r="AN14">
+        <v>-1.670498084291188</v>
+      </c>
+      <c r="AO14">
+        <v>-9.522388059701491</v>
+      </c>
+      <c r="AP14">
+        <v>5.218390804597702</v>
+      </c>
+      <c r="AQ14">
+        <v>-9.522388059701491</v>
       </c>
     </row>
     <row r="15">
@@ -2198,7 +2213,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GAM Holding AG (SWX:GAM)</t>
+          <t>Airesis SA (SWX:AIRE)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2207,34 +2222,34 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.148</v>
+        <v>0.0406</v>
       </c>
       <c r="G15">
-        <v>-0.03252918287937743</v>
+        <v>-0.03639395846444304</v>
       </c>
       <c r="H15">
-        <v>-0.03252918287937743</v>
+        <v>-0.03914411579609817</v>
       </c>
       <c r="I15">
-        <v>-0.01599221789883268</v>
+        <v>-0.05198237885462555</v>
       </c>
       <c r="J15">
-        <v>-0.01599221789883268</v>
+        <v>-0.05198237885462555</v>
       </c>
       <c r="K15">
-        <v>-1.08</v>
+        <v>0.664</v>
       </c>
       <c r="L15">
-        <v>-0.004202334630350195</v>
+        <v>0.004178728760226558</v>
       </c>
       <c r="M15">
-        <v>8.220000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="N15">
-        <v>0.03537005163511188</v>
+        <v>0.02637614678899082</v>
       </c>
       <c r="O15">
-        <v>-7.611111111111112</v>
+        <v>1.731927710843373</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2243,82 +2258,82 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
-        <v>8.220000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="T15">
         <v>1</v>
       </c>
       <c r="U15">
-        <v>270.5</v>
+        <v>6.97</v>
       </c>
       <c r="V15">
-        <v>1.16394148020654</v>
+        <v>0.1598623853211009</v>
       </c>
       <c r="W15">
-        <v>-0.002236487885690619</v>
+        <v>-0.08019323671497586</v>
       </c>
       <c r="X15">
-        <v>0.05171955815848092</v>
+        <v>0.1273939597388977</v>
       </c>
       <c r="Y15">
-        <v>-0.05395604604417154</v>
+        <v>-0.2075871964538736</v>
       </c>
       <c r="Z15">
-        <v>1.313905930470348</v>
+        <v>2.232682309962063</v>
       </c>
       <c r="AA15">
-        <v>-0.02101226993865031</v>
+        <v>-0.1160601376984684</v>
       </c>
       <c r="AB15">
-        <v>0.04493939351636422</v>
+        <v>0.07261546506607316</v>
       </c>
       <c r="AC15">
-        <v>-0.06595166345501453</v>
+        <v>-0.1886756027645416</v>
       </c>
       <c r="AD15">
-        <v>74.5</v>
+        <v>86.8</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>74.5</v>
+        <v>86.8</v>
       </c>
       <c r="AG15">
-        <v>-196</v>
+        <v>79.83</v>
       </c>
       <c r="AH15">
-        <v>0.2427500814597589</v>
+        <v>0.665644171779141</v>
       </c>
       <c r="AI15">
-        <v>0.1227145445560863</v>
+        <v>1.120433716277269</v>
       </c>
       <c r="AJ15">
-        <v>-5.384615384615384</v>
+        <v>0.6467633476464393</v>
       </c>
       <c r="AK15">
-        <v>-0.582293523469994</v>
+        <v>1.132340425531915</v>
       </c>
       <c r="AL15">
-        <v>6.49</v>
+        <v>3.83</v>
       </c>
       <c r="AM15">
-        <v>6.49</v>
+        <v>3.654</v>
       </c>
       <c r="AN15">
-        <v>76.56731757451182</v>
+        <v>-13.25190839694656</v>
       </c>
       <c r="AO15">
-        <v>-0.6332819722650231</v>
+        <v>-2.156657963446475</v>
       </c>
       <c r="AP15">
-        <v>-201.4388489208633</v>
+        <v>-12.18778625954199</v>
       </c>
       <c r="AQ15">
-        <v>-0.6332819722650231</v>
+        <v>-2.260536398467433</v>
       </c>
     </row>
     <row r="16">
@@ -2329,7 +2344,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Airesis SA (SWX:AIRE)</t>
+          <t>Genesis Growth Tech Acquisition Corp. (NasdaqGM:GGAA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2337,26 +2352,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>-0.00498</v>
-      </c>
-      <c r="G16">
-        <v>-0.131948608137045</v>
-      </c>
-      <c r="H16">
-        <v>-0.1349036402569593</v>
-      </c>
-      <c r="I16">
-        <v>-0.07566024268379729</v>
-      </c>
-      <c r="J16">
-        <v>-0.07566024268379729</v>
-      </c>
       <c r="K16">
-        <v>-12.5</v>
-      </c>
-      <c r="L16">
-        <v>-0.08922198429693076</v>
+        <v>-0.398</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2380,73 +2377,64 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>7.37</v>
+        <v>1.34</v>
       </c>
       <c r="V16">
-        <v>0.1497967479674797</v>
+        <v>0.004090354090354091</v>
       </c>
       <c r="W16">
-        <v>-320.5128205128205</v>
+        <v>39.8</v>
       </c>
       <c r="X16">
-        <v>0.09098652312265078</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y16">
-        <v>-320.6038070359431</v>
+        <v>39.7275457809593</v>
       </c>
       <c r="Z16">
-        <v>1.957825011528948</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>-0.1481295155046884</v>
+        <v>-6.116504854368932</v>
       </c>
       <c r="AB16">
-        <v>0.04417880398124217</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC16">
-        <v>-0.1923083194859306</v>
+        <v>-6.188959073409637</v>
       </c>
       <c r="AD16">
-        <v>94.7</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>94.7</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>87.33</v>
+        <v>-1.34</v>
       </c>
       <c r="AH16">
-        <v>0.6580958999305073</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1.114642184557439</v>
+        <v>-0</v>
       </c>
       <c r="AJ16">
-        <v>0.6396396396396397</v>
+        <v>-0.004107153803714829</v>
       </c>
       <c r="AK16">
-        <v>1.125531640675345</v>
+        <v>0.08792650918635171</v>
       </c>
       <c r="AL16">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>3.682</v>
-      </c>
-      <c r="AN16">
-        <v>-11.10199296600235</v>
-      </c>
-      <c r="AO16">
-        <v>-2.872628726287263</v>
-      </c>
-      <c r="AP16">
-        <v>-10.2379835873388</v>
+        <v>-1.49</v>
       </c>
       <c r="AQ16">
-        <v>-2.878870179250407</v>
+        <v>1.268456375838926</v>
       </c>
     </row>
     <row r="17">
@@ -2457,7 +2445,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VZ Holding AG (SWX:VZN)</t>
+          <t>VT5 Acquisition Company AG (SWX:VT5)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2465,318 +2453,68 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.094</v>
-      </c>
-      <c r="E17">
-        <v>0.0955</v>
-      </c>
-      <c r="G17">
-        <v>0.4200415368639668</v>
-      </c>
-      <c r="H17">
-        <v>0.4200415368639668</v>
-      </c>
-      <c r="I17">
-        <v>0.4262720664589824</v>
-      </c>
-      <c r="J17">
-        <v>0.3656745668153035</v>
-      </c>
       <c r="K17">
-        <v>139.6</v>
-      </c>
-      <c r="L17">
-        <v>0.3624091381100727</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>65.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.01567741168074224</v>
-      </c>
-      <c r="O17">
-        <v>0.4720630372492837</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>52.4</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.01246580230760081</v>
-      </c>
-      <c r="R17">
-        <v>0.3753581661891118</v>
+        <v>-0</v>
       </c>
       <c r="S17">
-        <v>13.50000000000001</v>
-      </c>
-      <c r="T17">
-        <v>0.2048558421851291</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1877.1</v>
+        <v>3.62</v>
       </c>
       <c r="V17">
-        <v>0.4465564410610205</v>
-      </c>
-      <c r="W17">
-        <v>0.2358108108108108</v>
+        <v>0.01635788522367827</v>
       </c>
       <c r="X17">
-        <v>0.04949220042627046</v>
-      </c>
-      <c r="Y17">
-        <v>0.1863186103845403</v>
-      </c>
-      <c r="Z17">
-        <v>-2.940458015267176</v>
-      </c>
-      <c r="AA17">
-        <v>-1.075250710971411</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB17">
-        <v>0.04395973371960109</v>
-      </c>
-      <c r="AC17">
-        <v>-1.119210444691012</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD17">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>-912.0999999999999</v>
+        <v>-3.62</v>
       </c>
       <c r="AH17">
-        <v>0.1867079423430396</v>
-      </c>
-      <c r="AI17">
-        <v>0.5871615454822026</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>-0.2771161207996597</v>
+        <v>-0.01662991547225285</v>
       </c>
       <c r="AK17">
-        <v>3.904537671232878</v>
+        <v>1</v>
       </c>
       <c r="AL17">
-        <v>0.485</v>
+        <v>0.344</v>
       </c>
       <c r="AM17">
-        <v>0.375</v>
-      </c>
-      <c r="AN17">
-        <v>5.623543123543124</v>
+        <v>0.251</v>
       </c>
       <c r="AO17">
-        <v>338.5567010309278</v>
-      </c>
-      <c r="AP17">
-        <v>-5.315268065268065</v>
+        <v>-14.15697674418605</v>
       </c>
       <c r="AQ17">
-        <v>437.8666666666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Talenthouse AG (SWX:NEWN)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K18">
-        <v>-1.1</v>
-      </c>
-      <c r="M18">
-        <v>-0</v>
-      </c>
-      <c r="N18">
-        <v>-0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>-0</v>
-      </c>
-      <c r="Q18">
-        <v>-0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0.075</v>
-      </c>
-      <c r="V18">
-        <v>0.002403846153846154</v>
-      </c>
-      <c r="W18">
-        <v>-8.270676691729324</v>
-      </c>
-      <c r="X18">
-        <v>0.04651681124091634</v>
-      </c>
-      <c r="Y18">
-        <v>-8.317193502970241</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>-8.666666666666666</v>
-      </c>
-      <c r="AB18">
-        <v>0.04455388182883832</v>
-      </c>
-      <c r="AC18">
-        <v>-8.711220548495504</v>
-      </c>
-      <c r="AD18">
-        <v>3.37</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>3.37</v>
-      </c>
-      <c r="AG18">
-        <v>3.295</v>
-      </c>
-      <c r="AH18">
-        <v>0.09748336708128436</v>
-      </c>
-      <c r="AI18">
-        <v>0.07129257457160991</v>
-      </c>
-      <c r="AJ18">
-        <v>0.09552109001304537</v>
-      </c>
-      <c r="AK18">
-        <v>0.069816717872656</v>
-      </c>
-      <c r="AL18">
-        <v>0.033</v>
-      </c>
-      <c r="AM18">
-        <v>0.029</v>
-      </c>
-      <c r="AO18">
-        <v>-35.45454545454545</v>
-      </c>
-      <c r="AQ18">
-        <v>-40.34482758620689</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>VT5 Acquisition Company AG (SWX:VT5)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>-386</v>
-      </c>
-      <c r="J19">
-        <v>-386</v>
-      </c>
-      <c r="K19">
-        <v>-0.772</v>
-      </c>
-      <c r="L19">
-        <v>-386</v>
-      </c>
-      <c r="M19">
-        <v>-0</v>
-      </c>
-      <c r="N19">
-        <v>-0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>-0</v>
-      </c>
-      <c r="Q19">
-        <v>-0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AB19">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
+        <v>-19.40239043824701</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ17"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0406</v>
+        <v>0.0294</v>
       </c>
       <c r="E2">
-        <v>0.14</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F2">
-        <v>0.07825</v>
+        <v>0.10185</v>
       </c>
       <c r="G2">
-        <v>0.2734956278116342</v>
+        <v>0.180352203085891</v>
       </c>
       <c r="H2">
-        <v>0.273155290773851</v>
+        <v>0.1800044992412854</v>
       </c>
       <c r="I2">
-        <v>0.2418707283487296</v>
+        <v>0.1945589045615963</v>
       </c>
       <c r="J2">
-        <v>0.2307689322074737</v>
+        <v>0.185201990326703</v>
       </c>
       <c r="K2">
-        <v>2224.867</v>
+        <v>2453.54</v>
       </c>
       <c r="L2">
-        <v>0.3008361717289041</v>
+        <v>0.316668630621196</v>
       </c>
       <c r="M2">
-        <v>2752.52212</v>
+        <v>2614.35656</v>
       </c>
       <c r="N2">
-        <v>0.06954765005369212</v>
+        <v>0.04805784831673413</v>
       </c>
       <c r="O2">
-        <v>1.237162544997072</v>
+        <v>1.065544706831762</v>
       </c>
       <c r="P2">
-        <v>1568.01412</v>
+        <v>1788.01056</v>
       </c>
       <c r="Q2">
-        <v>0.03961882685869497</v>
+        <v>0.03286772033926346</v>
       </c>
       <c r="R2">
-        <v>0.7047675748707675</v>
+        <v>0.7287472631381596</v>
       </c>
       <c r="S2">
-        <v>1184.508</v>
+        <v>826.3459999999999</v>
       </c>
       <c r="T2">
-        <v>0.4303355062592558</v>
+        <v>0.3160800682826522</v>
       </c>
       <c r="U2">
-        <v>31121.202</v>
+        <v>27018.413</v>
       </c>
       <c r="V2">
-        <v>0.786335721053629</v>
+        <v>0.4966601777199349</v>
       </c>
       <c r="W2">
-        <v>0.07931848016881786</v>
+        <v>-0.008675263774912075</v>
       </c>
       <c r="X2">
-        <v>0.07387315407617154</v>
+        <v>0.06307690478933353</v>
       </c>
       <c r="Y2">
-        <v>0.005445326092646322</v>
+        <v>-0.0717521685642456</v>
       </c>
       <c r="Z2">
-        <v>0.5837040225926845</v>
+        <v>1.182252755192657</v>
       </c>
       <c r="AA2">
-        <v>0.002432748538011695</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC2">
-        <v>-0.06830843328424305</v>
+        <v>-0.06227818370879545</v>
       </c>
       <c r="AD2">
-        <v>27509.62</v>
+        <v>26586.04</v>
       </c>
       <c r="AE2">
-        <v>0.1971135842615913</v>
+        <v>0.1493027358767875</v>
       </c>
       <c r="AF2">
-        <v>27509.81711358426</v>
+        <v>26586.18930273588</v>
       </c>
       <c r="AG2">
-        <v>-3611.384886415737</v>
+        <v>-432.2236972641222</v>
       </c>
       <c r="AH2">
-        <v>0.4100598786355984</v>
+        <v>0.3282797212177694</v>
       </c>
       <c r="AI2">
-        <v>0.7303138305138751</v>
+        <v>0.713924456572451</v>
       </c>
       <c r="AJ2">
-        <v>-0.1004107581541864</v>
+        <v>-0.008008892066649734</v>
       </c>
       <c r="AK2">
-        <v>-0.551585095770896</v>
+        <v>-0.04228745208309501</v>
       </c>
       <c r="AL2">
-        <v>17.56</v>
+        <v>30.323</v>
       </c>
       <c r="AM2">
-        <v>12.427</v>
+        <v>22.13</v>
       </c>
       <c r="AN2">
-        <v>15.41843613086627</v>
+        <v>17.32404902282762</v>
       </c>
       <c r="AO2">
-        <v>101.8660592255125</v>
+        <v>49.71193483494378</v>
       </c>
       <c r="AP2">
-        <v>-2.024088563025472</v>
+        <v>-0.2816464776338055</v>
       </c>
       <c r="AQ2">
-        <v>143.9420616399775</v>
+        <v>68.11635788522368</v>
       </c>
     </row>
     <row r="3">
@@ -725,112 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="E3">
-        <v>0.115</v>
+        <v>0.12</v>
       </c>
       <c r="G3">
-        <v>0.4455813953488372</v>
+        <v>0.3990089197224975</v>
       </c>
       <c r="H3">
-        <v>0.4455813953488372</v>
+        <v>0.3990089197224975</v>
       </c>
       <c r="I3">
-        <v>0.4316279069767442</v>
+        <v>0.442418235877106</v>
       </c>
       <c r="J3">
-        <v>0.3711673186008779</v>
+        <v>0.3803653191169375</v>
       </c>
       <c r="K3">
-        <v>158.4</v>
+        <v>179.6</v>
       </c>
       <c r="L3">
-        <v>0.3683720930232559</v>
+        <v>0.35599603567889</v>
       </c>
       <c r="M3">
-        <v>78.8</v>
+        <v>87.60000000000001</v>
       </c>
       <c r="N3">
-        <v>0.0258022265880812</v>
+        <v>0.01911244927346512</v>
       </c>
       <c r="O3">
-        <v>0.4974747474747475</v>
+        <v>0.4877505567928731</v>
       </c>
       <c r="P3">
-        <v>64.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.0212180746561886</v>
+        <v>0.01666884845311341</v>
       </c>
       <c r="R3">
-        <v>0.4090909090909091</v>
+        <v>0.4253897550111359</v>
       </c>
       <c r="S3">
-        <v>14</v>
+        <v>11.2</v>
       </c>
       <c r="T3">
-        <v>0.1776649746192893</v>
+        <v>0.1278538812785388</v>
       </c>
       <c r="U3">
-        <v>1770.3</v>
+        <v>1448.4</v>
       </c>
       <c r="V3">
-        <v>0.5796660117878193</v>
+        <v>0.3160099489461972</v>
       </c>
       <c r="W3">
-        <v>0.2349799732977303</v>
+        <v>0.2495137538205057</v>
       </c>
       <c r="X3">
-        <v>0.07997411874281787</v>
+        <v>0.0645847733880589</v>
       </c>
       <c r="Y3">
-        <v>0.1550058545549124</v>
+        <v>0.1849289804324468</v>
       </c>
       <c r="AB3">
-        <v>0.07115399820919299</v>
+        <v>0.06192490951974862</v>
       </c>
       <c r="AD3">
-        <v>832.2</v>
+        <v>519.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>832.2</v>
+        <v>519.7</v>
       </c>
       <c r="AG3">
-        <v>-938.0999999999999</v>
+        <v>-928.7</v>
       </c>
       <c r="AH3">
-        <v>0.2141423498533272</v>
+        <v>0.1018400580039584</v>
       </c>
       <c r="AI3">
-        <v>0.5349016583108368</v>
+        <v>0.368921700858948</v>
       </c>
       <c r="AJ3">
-        <v>-0.4433574365518219</v>
+        <v>-0.2541111445535886</v>
       </c>
       <c r="AK3">
-        <v>4.373426573426575</v>
+        <v>23.39294710327453</v>
       </c>
       <c r="AL3">
-        <v>0.674</v>
+        <v>13.1</v>
       </c>
       <c r="AM3">
-        <v>0.65</v>
+        <v>12.55</v>
       </c>
       <c r="AN3">
-        <v>4.289690721649484</v>
+        <v>2.22951522951523</v>
       </c>
       <c r="AO3">
-        <v>275.3709198813056</v>
+        <v>17.0381679389313</v>
       </c>
       <c r="AP3">
-        <v>-4.835567010309278</v>
+        <v>-3.984126984126985</v>
       </c>
       <c r="AQ3">
-        <v>285.5384615384615</v>
+        <v>17.78486055776893</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Partners Group Holding AG (SWX:PGHN)</t>
+          <t>Q Capital AG (BRSE:QCAP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,125 +849,86 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.169</v>
-      </c>
-      <c r="E4">
-        <v>0.144</v>
-      </c>
-      <c r="F4">
-        <v>0.0603</v>
-      </c>
       <c r="G4">
-        <v>0.737037335698734</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.737037335698734</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.6436980888638013</v>
+        <v>0.6617179215270413</v>
       </c>
       <c r="J4">
-        <v>0.5487434400583017</v>
+        <v>0.6617179215270413</v>
       </c>
       <c r="K4">
-        <v>1359.8</v>
+        <v>-4.84</v>
       </c>
       <c r="L4">
-        <v>0.5482622369163778</v>
+        <v>-5.132555673382821</v>
       </c>
       <c r="M4">
-        <v>1551.9</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.06736554238833181</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.141270775113987</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>901.7</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.03914138125623996</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.663112222385645</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>650.2</v>
-      </c>
-      <c r="T4">
-        <v>0.418970294477737</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>321.8</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.01396883274731953</v>
-      </c>
-      <c r="W4">
-        <v>0.569168306056674</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.07387315407617154</v>
-      </c>
-      <c r="Y4">
-        <v>0.4952951519805024</v>
-      </c>
-      <c r="Z4">
-        <v>0.8690259285213734</v>
-      </c>
-      <c r="AA4">
-        <v>0.4768722775166783</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB4">
-        <v>0.07215729279577085</v>
-      </c>
-      <c r="AC4">
-        <v>0.4047149847209074</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD4">
-        <v>1184.5</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1184.5</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>862.7</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.04890283425881965</v>
-      </c>
-      <c r="AI4">
-        <v>0.3522990898816252</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.03609668740611807</v>
-      </c>
-      <c r="AK4">
-        <v>0.2837455597947639</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>8.17</v>
+        <v>0.001</v>
       </c>
       <c r="AM4">
-        <v>4.82</v>
-      </c>
-      <c r="AN4">
-        <v>0.7364919480196481</v>
+        <v>0.001</v>
       </c>
       <c r="AO4">
-        <v>195.4100367197063</v>
-      </c>
-      <c r="AP4">
-        <v>0.5364048995834111</v>
+        <v>624</v>
       </c>
       <c r="AQ4">
-        <v>331.2240663900415</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AP Alternative Portfolio AG (BRSE:APN)</t>
+          <t>Partners Group Holding AG (SWX:PGHN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,109 +948,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.147</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="E5">
-        <v>0.14</v>
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.143</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.542106188466948</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.542106188466948</v>
       </c>
       <c r="I5">
-        <v>0.904040404040404</v>
+        <v>0.5922116736990155</v>
       </c>
       <c r="J5">
-        <v>0.904040404040404</v>
+        <v>0.5212180353776246</v>
       </c>
       <c r="K5">
-        <v>14.2</v>
+        <v>1220.2</v>
       </c>
       <c r="L5">
-        <v>0.7171717171717171</v>
+        <v>0.536304500703235</v>
       </c>
       <c r="M5">
-        <v>21.54</v>
+        <v>1318.5</v>
       </c>
       <c r="N5">
-        <v>0.4929061784897025</v>
+        <v>0.03529279502340808</v>
       </c>
       <c r="O5">
-        <v>1.516901408450704</v>
+        <v>1.080560563841993</v>
       </c>
       <c r="P5">
-        <v>2.84</v>
+        <v>1071.9</v>
       </c>
       <c r="Q5">
-        <v>0.06498855835240273</v>
+        <v>0.02869195827500275</v>
       </c>
       <c r="R5">
-        <v>0.2</v>
+        <v>0.8784625471234224</v>
       </c>
       <c r="S5">
-        <v>18.7</v>
+        <v>246.5999999999999</v>
       </c>
       <c r="T5">
-        <v>0.8681522748375116</v>
+        <v>0.1870307167235494</v>
       </c>
       <c r="U5">
-        <v>3.01</v>
+        <v>405.5</v>
       </c>
       <c r="V5">
-        <v>0.06887871853546911</v>
+        <v>0.01085417397193172</v>
       </c>
       <c r="W5">
-        <v>0.1865965834428384</v>
+        <v>0.5603159296505488</v>
       </c>
       <c r="X5">
-        <v>0.07245421904070486</v>
+        <v>0.06307690478933353</v>
       </c>
       <c r="Y5">
-        <v>0.1141423644021335</v>
+        <v>0.4972390248612152</v>
       </c>
       <c r="Z5">
-        <v>0.3</v>
+        <v>0.7483225891330089</v>
       </c>
       <c r="AA5">
-        <v>0.2712121212121212</v>
+        <v>0.3900392297366042</v>
       </c>
       <c r="AB5">
-        <v>0.07245421904070486</v>
+        <v>0.06235255522058399</v>
       </c>
       <c r="AC5">
-        <v>0.1987579021714163</v>
+        <v>0.3276866745160202</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1430.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1430.1</v>
       </c>
       <c r="AG5">
-        <v>-3.01</v>
+        <v>1024.6</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.03686869988914383</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.3892381807789663</v>
       </c>
       <c r="AJ5">
-        <v>-0.07397394937331038</v>
+        <v>0.02669376164237237</v>
       </c>
       <c r="AK5">
-        <v>-0.05226601840597325</v>
+        <v>0.3134675396194089</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>8.49</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>4.69</v>
+      </c>
+      <c r="AN5">
+        <v>1.053170336549083</v>
+      </c>
+      <c r="AO5">
+        <v>158.7043580683157</v>
+      </c>
+      <c r="AP5">
+        <v>0.7545474629943294</v>
+      </c>
+      <c r="AQ5">
+        <v>287.2921108742004</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Matador Partners Group AG (BRSE:SQL)</t>
+          <t>nebag ag (SWX:NBEN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1108,116 +1084,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0294</v>
+      </c>
       <c r="G6">
-        <v>0.6104651162790697</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.6104651162790697</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.8430232558139535</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J6">
-        <v>0.7719324887191947</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K6">
-        <v>12.2</v>
+        <v>-0.74</v>
       </c>
       <c r="L6">
-        <v>0.7093023255813954</v>
+        <v>-0.2868217054263566</v>
       </c>
       <c r="M6">
-        <v>7.06</v>
+        <v>17.80976</v>
       </c>
       <c r="N6">
-        <v>0.108282208588957</v>
+        <v>0.2193320197044335</v>
       </c>
       <c r="O6">
-        <v>0.578688524590164</v>
+        <v>-24.06724324324324</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>5.909759999999999</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.07278029556650245</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>-7.986162162162161</v>
       </c>
       <c r="S6">
-        <v>7.06</v>
+        <v>11.9</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0.6681729568506258</v>
       </c>
       <c r="U6">
-        <v>1.18</v>
+        <v>7.64</v>
       </c>
       <c r="V6">
-        <v>0.01809815950920245</v>
+        <v>0.0940886699507389</v>
       </c>
       <c r="W6">
-        <v>0.2505133470225873</v>
+        <v>-0.008675263774912075</v>
       </c>
       <c r="X6">
-        <v>0.08261242503335933</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y6">
-        <v>0.1679009219892279</v>
+        <v>-0.07098365231071371</v>
       </c>
       <c r="Z6">
-        <v>0.2527924750146972</v>
+        <v>0.03426294820717132</v>
       </c>
       <c r="AA6">
-        <v>0.1951387243675801</v>
+        <v>0.02284196547144754</v>
       </c>
       <c r="AB6">
-        <v>0.07082056179568418</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC6">
-        <v>0.1243181625718959</v>
+        <v>-0.03946642306435409</v>
       </c>
       <c r="AD6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>22.82</v>
+        <v>-7.64</v>
       </c>
       <c r="AH6">
-        <v>0.2690582959641256</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.2891566265060241</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0.2592592592592592</v>
+        <v>-0.1038607939097335</v>
       </c>
       <c r="AK6">
-        <v>0.2789049132241506</v>
+        <v>-0.09966084007304983</v>
       </c>
       <c r="AL6">
-        <v>0.9350000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AM6">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="AN6">
-        <v>1.655172413793103</v>
+        <v>0.14</v>
       </c>
       <c r="AO6">
-        <v>15.50802139037433</v>
-      </c>
-      <c r="AP6">
-        <v>1.573793103448276</v>
+        <v>12.28571428571428</v>
       </c>
       <c r="AQ6">
-        <v>15.50802139037433</v>
+        <v>12.28571428571428</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alpine Select AG (SWX:ALPN)</t>
+          <t>Matador Partners Group AG (BRSE:SQL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1236,119 +1209,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.247</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>4.062499999999999</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>4.062499999999999</v>
       </c>
       <c r="I7">
-        <v>0.8798829605385354</v>
+        <v>0.4375</v>
       </c>
       <c r="J7">
-        <v>0.8798829605385354</v>
+        <v>0.4375</v>
       </c>
       <c r="K7">
-        <v>-13.4</v>
+        <v>-3.8</v>
       </c>
       <c r="L7">
-        <v>-0.6473429951690821</v>
+        <v>-1.826923076923077</v>
       </c>
       <c r="M7">
-        <v>9.907999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="N7">
-        <v>0.08548748921484037</v>
+        <v>0.009073825503355705</v>
       </c>
       <c r="O7">
-        <v>-0.7394029850746268</v>
+        <v>-0.1778947368421053</v>
       </c>
       <c r="P7">
-        <v>9.279999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.0800690250215703</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0.6925373134328358</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>0.6280000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="T7">
-        <v>0.06338312474767865</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>2.94</v>
+        <v>0.181</v>
       </c>
       <c r="V7">
-        <v>0.02536669542709232</v>
+        <v>0.002429530201342282</v>
       </c>
       <c r="W7">
-        <v>-0.09745454545454546</v>
+        <v>-0.06440677966101695</v>
       </c>
       <c r="X7">
-        <v>0.07642989825285378</v>
+        <v>0.07165929973301288</v>
       </c>
       <c r="Y7">
-        <v>-0.1738844437073992</v>
+        <v>-0.1360660793940298</v>
       </c>
       <c r="Z7">
-        <v>0.1498402642149611</v>
+        <v>0.02542165729650453</v>
       </c>
       <c r="AA7">
-        <v>0.1318418952853363</v>
+        <v>0.01112197506722073</v>
       </c>
       <c r="AB7">
-        <v>0.07168964088305164</v>
+        <v>0.06111184142407931</v>
       </c>
       <c r="AC7">
-        <v>0.06015225440228468</v>
+        <v>-0.04998986635685858</v>
       </c>
       <c r="AD7">
-        <v>16.5</v>
+        <v>34.7</v>
       </c>
       <c r="AE7">
-        <v>0.1971135842615913</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>16.69711358426159</v>
+        <v>34.7</v>
       </c>
       <c r="AG7">
-        <v>13.75711358426159</v>
+        <v>34.51900000000001</v>
       </c>
       <c r="AH7">
-        <v>0.1259236580112361</v>
+        <v>0.3177655677655678</v>
       </c>
       <c r="AI7">
-        <v>0.1223257631301795</v>
+        <v>0.3607068607068607</v>
       </c>
       <c r="AJ7">
-        <v>0.1061038087611068</v>
+        <v>0.3166328805070676</v>
       </c>
       <c r="AK7">
-        <v>0.1030054724534173</v>
+        <v>0.3595017652756226</v>
       </c>
       <c r="AL7">
-        <v>0.119</v>
+        <v>1.24</v>
       </c>
       <c r="AM7">
-        <v>0.119</v>
+        <v>1.24</v>
       </c>
       <c r="AN7">
-        <v>311.3207547169811</v>
+        <v>38.13186813186813</v>
       </c>
       <c r="AO7">
-        <v>152.9411764705882</v>
+        <v>0.7338709677419355</v>
       </c>
       <c r="AP7">
-        <v>259.5681808351243</v>
+        <v>37.93296703296703</v>
       </c>
       <c r="AQ7">
-        <v>152.9411764705882</v>
+        <v>0.7338709677419355</v>
       </c>
     </row>
     <row r="8">
@@ -1359,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nebag ag (SWX:NBEN)</t>
+          <t>Julius Bär Gruppe AG (SWX:BAER)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1368,7 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.00728</v>
+        <v>0.031</v>
+      </c>
+      <c r="E8">
+        <v>0.0532</v>
+      </c>
+      <c r="F8">
+        <v>0.0607</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,103 +1353,97 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.68359375</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.68359375</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>-2.36</v>
+        <v>1151.9</v>
       </c>
       <c r="L8">
-        <v>-0.9218749999999999</v>
+        <v>0.256553598075681</v>
       </c>
       <c r="M8">
-        <v>9.784120000000001</v>
+        <v>877.4</v>
       </c>
       <c r="N8">
-        <v>0.117315587529976</v>
+        <v>0.07606547144293789</v>
       </c>
       <c r="O8">
-        <v>-4.145813559322034</v>
+        <v>0.7616980640680614</v>
       </c>
       <c r="P8">
-        <v>4.784120000000001</v>
+        <v>598.5</v>
       </c>
       <c r="Q8">
-        <v>0.05736354916067147</v>
+        <v>0.05188646530499012</v>
       </c>
       <c r="R8">
-        <v>-2.027169491525424</v>
+        <v>0.5195763521138987</v>
       </c>
       <c r="S8">
-        <v>5.000000000000001</v>
+        <v>278.9</v>
       </c>
       <c r="T8">
-        <v>0.5110321623201678</v>
+        <v>0.3178709824481422</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>25023.7</v>
       </c>
       <c r="V8">
-        <v>0.1199040767386091</v>
+        <v>2.169409092485349</v>
       </c>
       <c r="W8">
-        <v>-0.02471204188481675</v>
+        <v>0.1807781038622703</v>
       </c>
       <c r="X8">
-        <v>0.07245421904070486</v>
+        <v>0.104874074751403</v>
       </c>
       <c r="Y8">
-        <v>-0.09716626092552161</v>
+        <v>0.07590402911086733</v>
       </c>
       <c r="Z8">
-        <v>0.03114355231143552</v>
+        <v>1.527332721025956</v>
       </c>
       <c r="AA8">
-        <v>0.02128953771289538</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07245421904070486</v>
+        <v>0.05974969642463069</v>
       </c>
       <c r="AC8">
-        <v>-0.05116468132780948</v>
+        <v>-0.05974969642463069</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>24456.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>24456.2</v>
       </c>
       <c r="AG8">
-        <v>-10</v>
+        <v>-567.5</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.679508766080409</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.777792266029749</v>
       </c>
       <c r="AJ8">
-        <v>-0.1362397820163488</v>
+        <v>-0.05174473206714506</v>
       </c>
       <c r="AK8">
-        <v>-0.1328021248339973</v>
+        <v>-0.08840390067607565</v>
       </c>
       <c r="AL8">
-        <v>0.138</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.138</v>
-      </c>
-      <c r="AO8">
-        <v>12.68115942028985</v>
-      </c>
-      <c r="AQ8">
-        <v>12.68115942028985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1454,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Varia Europe Properties AG (BRSE:VARE)</t>
+          <t>Bellevue Group AG (SWX:BBN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1492,98 +1462,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>-0.0307</v>
+      </c>
+      <c r="E9">
+        <v>-0.0389</v>
+      </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.02297830374753452</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.6358024691358024</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.6358024691358024</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>1.29</v>
+        <v>21.3</v>
       </c>
       <c r="L9">
-        <v>0.7962962962962963</v>
+        <v>0.2100591715976331</v>
       </c>
       <c r="M9">
-        <v>1.47</v>
+        <v>13.89</v>
       </c>
       <c r="N9">
-        <v>0.04375</v>
+        <v>0.03611544461778471</v>
       </c>
       <c r="O9">
-        <v>1.13953488372093</v>
+        <v>0.652112676056338</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>4.45</v>
       </c>
       <c r="Q9">
-        <v>0.04375</v>
+        <v>0.01157046281851274</v>
       </c>
       <c r="R9">
-        <v>1.13953488372093</v>
+        <v>0.2089201877934272</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>9.440000000000001</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.6796256299496041</v>
       </c>
       <c r="U9">
-        <v>0.542</v>
+        <v>17</v>
       </c>
       <c r="V9">
-        <v>0.01613095238095238</v>
+        <v>0.04420176807072283</v>
       </c>
       <c r="W9">
-        <v>0.02504854368932039</v>
+        <v>0.1609977324263039</v>
       </c>
       <c r="X9">
-        <v>0.07245421904070486</v>
+        <v>0.06247073089006003</v>
       </c>
       <c r="Y9">
-        <v>-0.04740567535138447</v>
+        <v>0.09852700153624383</v>
       </c>
       <c r="Z9">
-        <v>0.03177031240807202</v>
+        <v>1.90172543135784</v>
       </c>
       <c r="AA9">
-        <v>0.02019964307426801</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07245421904070486</v>
+        <v>0.06227818370879545</v>
       </c>
       <c r="AC9">
-        <v>-0.05225457596643684</v>
+        <v>-0.06227818370879545</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AG9">
-        <v>-0.542</v>
+        <v>-13.89</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.008021459338165123</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.02338170062401323</v>
       </c>
       <c r="AJ9">
-        <v>-0.01639542622058201</v>
+        <v>-0.03746864125596828</v>
       </c>
       <c r="AK9">
-        <v>-0.01213668323704599</v>
+        <v>-0.1197310576674425</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1600,7 +1576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Julius Bär Gruppe AG (SWX:BAER)</t>
+          <t>One Swiss Bank SA (SWX:ONE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1609,13 +1585,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0432</v>
+        <v>0.255</v>
       </c>
       <c r="E10">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="F10">
-        <v>0.09619999999999999</v>
+        <v>0.442</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1630,90 +1603,96 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>970.6</v>
+        <v>8.18</v>
       </c>
       <c r="L10">
-        <v>0.248489503328213</v>
+        <v>0.1770562770562771</v>
       </c>
       <c r="M10">
-        <v>1043.8</v>
+        <v>2.6208</v>
       </c>
       <c r="N10">
-        <v>0.08879701230976018</v>
+        <v>0.04844362292051756</v>
       </c>
       <c r="O10">
-        <v>1.075417267669483</v>
+        <v>0.3203911980440098</v>
       </c>
       <c r="P10">
-        <v>580.3</v>
+        <v>2.6208</v>
       </c>
       <c r="Q10">
-        <v>0.04936664710035815</v>
+        <v>0.04844362292051756</v>
       </c>
       <c r="R10">
-        <v>0.5978776014836183</v>
+        <v>0.3203911980440098</v>
       </c>
       <c r="S10">
-        <v>463.5</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.4440505844031424</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>28735.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>2.444546529532365</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>0.1335884166483153</v>
+        <v>0.1821826280623608</v>
       </c>
       <c r="X10">
-        <v>0.1318574242478292</v>
+        <v>0.06368885673121047</v>
       </c>
       <c r="Y10">
-        <v>0.001730992400486131</v>
+        <v>0.1184937713311503</v>
       </c>
       <c r="Z10">
-        <v>0.4432893751276754</v>
+        <v>0.9352226720647774</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06830843328424305</v>
+        <v>0.06238546145898455</v>
       </c>
       <c r="AC10">
-        <v>-0.06830843328424305</v>
+        <v>-0.06238546145898455</v>
       </c>
       <c r="AD10">
-        <v>25303.2</v>
+        <v>3.72</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>25303.2</v>
+        <v>3.72</v>
       </c>
       <c r="AG10">
-        <v>-3432.200000000001</v>
+        <v>3.72</v>
       </c>
       <c r="AH10">
-        <v>0.6827980927246675</v>
+        <v>0.06433759944655829</v>
       </c>
       <c r="AI10">
-        <v>0.7987474193935339</v>
+        <v>0.06512605042016807</v>
       </c>
       <c r="AJ10">
-        <v>-0.4123902099078425</v>
+        <v>0.06433759944655829</v>
       </c>
       <c r="AK10">
-        <v>-1.166145691764067</v>
+        <v>0.06512605042016807</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.598</v>
       </c>
       <c r="AM10">
+        <v>0.598</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
         <v>0</v>
       </c>
     </row>
@@ -1725,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spice Private Equity AG (SWX:SPCE)</t>
+          <t>Alpine Select AG (SWX:ALPN)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1734,7 +1713,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.111</v>
+        <v>-0.475</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1743,97 +1722,109 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.05430809399477807</v>
+        <v>-0.3315596311725183</v>
       </c>
       <c r="J11">
-        <v>0.05430809399477807</v>
+        <v>-0.3315596311725183</v>
       </c>
       <c r="K11">
-        <v>0.141</v>
+        <v>-4.14</v>
       </c>
       <c r="L11">
-        <v>0.03681462140992166</v>
+        <v>-2.338983050847458</v>
       </c>
       <c r="M11">
-        <v>8.539999999999999</v>
+        <v>11.75</v>
       </c>
       <c r="N11">
-        <v>0.1113428943937418</v>
+        <v>0.1447044334975369</v>
       </c>
       <c r="O11">
-        <v>60.56737588652482</v>
+        <v>-2.83816425120773</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>9.73</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.1198275862068966</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>-2.35024154589372</v>
       </c>
       <c r="S11">
-        <v>8.539999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.1719148936170213</v>
       </c>
       <c r="U11">
-        <v>45.5</v>
+        <v>18.8</v>
       </c>
       <c r="V11">
-        <v>0.5932203389830508</v>
+        <v>0.2315270935960591</v>
       </c>
       <c r="W11">
-        <v>0.0009227748691099474</v>
+        <v>-0.03654015887025595</v>
       </c>
       <c r="X11">
-        <v>0.07245421904070486</v>
+        <v>0.06234530265135188</v>
       </c>
       <c r="Y11">
-        <v>-0.0715314441715949</v>
+        <v>-0.09888546152160783</v>
       </c>
       <c r="Z11">
-        <v>0.0447953216374269</v>
+        <v>0.01393598706451304</v>
       </c>
       <c r="AA11">
-        <v>0.002432748538011695</v>
+        <v>-0.00462061073113493</v>
       </c>
       <c r="AB11">
-        <v>0.07245421904070486</v>
+        <v>0.06230147759938214</v>
       </c>
       <c r="AC11">
-        <v>-0.07002147050269317</v>
+        <v>-0.06692208833051708</v>
       </c>
       <c r="AD11">
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.1493027358767875</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>0.1493027358767875</v>
       </c>
       <c r="AG11">
-        <v>-45.5</v>
+        <v>-18.65069726412321</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.001835329017650471</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.001343262910353783</v>
       </c>
       <c r="AJ11">
-        <v>-1.458333333333333</v>
+        <v>-0.298175941990567</v>
       </c>
       <c r="AK11">
-        <v>-0.4600606673407482</v>
+        <v>-0.2019581817251513</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.154</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>-3.954545454545455</v>
+      </c>
+      <c r="AP11">
+        <v>-358.6672550792926</v>
+      </c>
+      <c r="AQ11">
+        <v>-3.954545454545455</v>
       </c>
     </row>
     <row r="12">
@@ -1844,7 +1835,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bellevue Group AG (SWX:BBN)</t>
+          <t>Varia Europe Properties AG (BRSE:VARE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1852,104 +1843,83 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.034</v>
-      </c>
-      <c r="E12">
-        <v>0.428</v>
-      </c>
-      <c r="G12">
-        <v>0.01753794266441821</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
       <c r="K12">
-        <v>36.5</v>
-      </c>
-      <c r="L12">
-        <v>0.3077571669477235</v>
+        <v>-4.62</v>
       </c>
       <c r="M12">
-        <v>13.44</v>
+        <v>18.5</v>
       </c>
       <c r="N12">
-        <v>0.02497212931995541</v>
+        <v>0.7805907172995781</v>
       </c>
       <c r="O12">
-        <v>0.3682191780821918</v>
+        <v>-4.004329004329004</v>
       </c>
       <c r="P12">
-        <v>2.84</v>
+        <v>18.5</v>
       </c>
       <c r="Q12">
-        <v>0.005276848755109624</v>
+        <v>0.7805907172995781</v>
       </c>
       <c r="R12">
-        <v>0.07780821917808219</v>
+        <v>-4.004329004329004</v>
       </c>
       <c r="S12">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>0.7886904761904762</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>38.8</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
-        <v>0.07209215904868077</v>
+        <v>0.1181434599156118</v>
       </c>
       <c r="W12">
-        <v>0.2581329561527581</v>
+        <v>-0.102212389380531</v>
       </c>
       <c r="X12">
-        <v>0.0726039434221078</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y12">
-        <v>0.1855290127306503</v>
+        <v>-0.1645207779163326</v>
       </c>
       <c r="Z12">
-        <v>2.840038314176245</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>-0.05239822652156388</v>
       </c>
       <c r="AB12">
-        <v>0.0724214545198448</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC12">
-        <v>-0.0724214545198448</v>
+        <v>-0.1147066150573655</v>
       </c>
       <c r="AD12">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>-35.88</v>
+        <v>-2.8</v>
       </c>
       <c r="AH12">
-        <v>0.005396215257244234</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>0.02159443869250111</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>-0.07142857142857141</v>
+        <v>-0.1339712918660287</v>
       </c>
       <c r="AK12">
-        <v>-0.3721219663970129</v>
+        <v>-0.125</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1966,7 +1936,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>One Swiss Bank SA (SWX:ONE)</t>
+          <t>Airesis SA (SWX:AIRE)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1975,25 +1945,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.215</v>
+        <v>-0.00187</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-0.03779975278121137</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>-0.04004944375772559</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-0.06860321384425215</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>-0.06860321384425215</v>
       </c>
       <c r="K13">
-        <v>-2.97</v>
+        <v>-14.9</v>
       </c>
       <c r="L13">
-        <v>-0.08761061946902655</v>
+        <v>-0.09208899876390605</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2017,61 +1987,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>0.992</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.02106157112526539</v>
       </c>
       <c r="W13">
-        <v>-0.04706814580031696</v>
+        <v>1.925064599483204</v>
       </c>
       <c r="X13">
-        <v>0.09104674903446375</v>
+        <v>0.1037394527033314</v>
       </c>
       <c r="Y13">
-        <v>-0.1381148948347807</v>
+        <v>1.821325146779873</v>
       </c>
       <c r="Z13">
-        <v>0.5295220243673852</v>
+        <v>2.510083772882408</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>-0.1721998138380391</v>
       </c>
       <c r="AB13">
-        <v>0.07380601714464163</v>
+        <v>0.06311532048736596</v>
       </c>
       <c r="AC13">
-        <v>-0.07380601714464163</v>
+        <v>-0.235315134325405</v>
       </c>
       <c r="AD13">
-        <v>15.9</v>
+        <v>97.2</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>15.9</v>
+        <v>97.2</v>
       </c>
       <c r="AG13">
-        <v>15.9</v>
+        <v>96.208</v>
       </c>
       <c r="AH13">
-        <v>0.4025316455696203</v>
+        <v>0.6735966735966735</v>
       </c>
       <c r="AI13">
-        <v>0.2615131578947368</v>
+        <v>1.294274300932091</v>
       </c>
       <c r="AJ13">
-        <v>0.4025316455696203</v>
+        <v>0.6713372596086751</v>
       </c>
       <c r="AK13">
-        <v>0.2615131578947368</v>
+        <v>1.298213418254439</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>4.647</v>
+      </c>
+      <c r="AN13">
+        <v>-9.888097660223805</v>
+      </c>
+      <c r="AO13">
+        <v>-2.361702127659574</v>
+      </c>
+      <c r="AP13">
+        <v>-9.787182095625635</v>
+      </c>
+      <c r="AQ13">
+        <v>-2.388637830858618</v>
       </c>
     </row>
     <row r="14">
@@ -2091,34 +2073,34 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.172</v>
+        <v>-0.243</v>
       </c>
       <c r="G14">
-        <v>-0.01843796342066238</v>
+        <v>-0.2599009900990099</v>
       </c>
       <c r="H14">
-        <v>-0.01843796342066238</v>
+        <v>-0.2599009900990099</v>
       </c>
       <c r="I14">
-        <v>-0.1576866040533861</v>
+        <v>-0.3100247524752475</v>
       </c>
       <c r="J14">
-        <v>-0.1576866040533861</v>
+        <v>-0.3100247524752475</v>
       </c>
       <c r="K14">
-        <v>-309.8</v>
+        <v>-96.09999999999999</v>
       </c>
       <c r="L14">
-        <v>-1.531389026198715</v>
+        <v>-0.5946782178217822</v>
       </c>
       <c r="M14">
-        <v>5.13</v>
+        <v>2.01</v>
       </c>
       <c r="N14">
-        <v>0.03230478589420654</v>
+        <v>0.02727272727272727</v>
       </c>
       <c r="O14">
-        <v>-0.01655907036797934</v>
+        <v>-0.02091571279916753</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2130,79 +2112,79 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>5.13</v>
+        <v>2.01</v>
       </c>
       <c r="T14">
         <v>1</v>
       </c>
       <c r="U14">
-        <v>179.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="V14">
-        <v>1.132241813602015</v>
+        <v>1.26729986431479</v>
       </c>
       <c r="W14">
-        <v>-0.5816748028539241</v>
+        <v>-0.4496958352831071</v>
       </c>
       <c r="X14">
-        <v>0.08003108074815624</v>
+        <v>0.07293213871997273</v>
       </c>
       <c r="Y14">
-        <v>-0.6617058836020804</v>
+        <v>-0.5226279740030799</v>
       </c>
       <c r="Z14">
-        <v>0.601010101010101</v>
+        <v>2.08516129032258</v>
       </c>
       <c r="AA14">
-        <v>-0.09477124183006534</v>
+        <v>-0.6464516129032258</v>
       </c>
       <c r="AB14">
-        <v>0.07250640129845459</v>
+        <v>0.06272293925165918</v>
       </c>
       <c r="AC14">
-        <v>-0.1672776431285199</v>
+        <v>-0.709174552154885</v>
       </c>
       <c r="AD14">
-        <v>43.6</v>
+        <v>39</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>43.6</v>
+        <v>39</v>
       </c>
       <c r="AG14">
-        <v>-136.2</v>
+        <v>-54.40000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.2154150197628459</v>
+        <v>0.3460514640638864</v>
       </c>
       <c r="AI14">
-        <v>0.1694520015546055</v>
+        <v>0.2906110283159464</v>
       </c>
       <c r="AJ14">
-        <v>-6.026548672566374</v>
+        <v>-2.818652849740933</v>
       </c>
       <c r="AK14">
-        <v>-1.75741935483871</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AL14">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="AM14">
-        <v>3.35</v>
+        <v>1.9</v>
       </c>
       <c r="AN14">
-        <v>-1.670498084291188</v>
+        <v>-0.8210526315789474</v>
       </c>
       <c r="AO14">
-        <v>-9.522388059701491</v>
+        <v>-26.36842105263158</v>
       </c>
       <c r="AP14">
-        <v>5.218390804597702</v>
+        <v>1.145263157894737</v>
       </c>
       <c r="AQ14">
-        <v>-9.522388059701491</v>
+        <v>-26.36842105263158</v>
       </c>
     </row>
     <row r="15">
@@ -2213,7 +2195,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airesis SA (SWX:AIRE)</t>
+          <t>Genesis Growth Tech Acquisition Corp. (OTCPK:GGAA.F)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2221,35 +2203,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.0406</v>
-      </c>
-      <c r="G15">
-        <v>-0.03639395846444304</v>
-      </c>
-      <c r="H15">
-        <v>-0.03914411579609817</v>
-      </c>
-      <c r="I15">
-        <v>-0.05198237885462555</v>
-      </c>
-      <c r="J15">
-        <v>-0.05198237885462555</v>
-      </c>
       <c r="K15">
-        <v>0.664</v>
-      </c>
-      <c r="L15">
-        <v>0.004178728760226558</v>
+        <v>1.5</v>
       </c>
       <c r="M15">
-        <v>1.15</v>
+        <v>263.6</v>
       </c>
       <c r="N15">
-        <v>0.02637614678899082</v>
+        <v>3.486772486772487</v>
       </c>
       <c r="O15">
-        <v>1.731927710843373</v>
+        <v>175.7333333333333</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2261,260 +2225,61 @@
         <v>-0</v>
       </c>
       <c r="S15">
-        <v>1.15</v>
+        <v>263.6</v>
       </c>
       <c r="T15">
         <v>1</v>
       </c>
       <c r="U15">
-        <v>6.97</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>0.1598623853211009</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>-0.08019323671497586</v>
+        <v>-0.1079136690647482</v>
       </c>
       <c r="X15">
-        <v>0.1273939597388977</v>
+        <v>0.06292182687442752</v>
       </c>
       <c r="Y15">
-        <v>-0.2075871964538736</v>
-      </c>
-      <c r="Z15">
-        <v>2.232682309962063</v>
-      </c>
-      <c r="AA15">
-        <v>-0.1160601376984684</v>
+        <v>-0.1708354959391757</v>
       </c>
       <c r="AB15">
-        <v>0.07261546506607316</v>
-      </c>
-      <c r="AC15">
-        <v>-0.1886756027645416</v>
+        <v>0.06234390712882455</v>
       </c>
       <c r="AD15">
-        <v>86.8</v>
+        <v>2.31</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>86.8</v>
+        <v>2.31</v>
       </c>
       <c r="AG15">
-        <v>79.83</v>
+        <v>2.31</v>
       </c>
       <c r="AH15">
-        <v>0.665644171779141</v>
+        <v>0.02964959568733154</v>
       </c>
       <c r="AI15">
-        <v>1.120433716277269</v>
+        <v>-0.8619402985074627</v>
       </c>
       <c r="AJ15">
-        <v>0.6467633476464393</v>
+        <v>0.02964959568733154</v>
       </c>
       <c r="AK15">
-        <v>1.132340425531915</v>
+        <v>-0.8619402985074627</v>
       </c>
       <c r="AL15">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>3.654</v>
-      </c>
-      <c r="AN15">
-        <v>-13.25190839694656</v>
-      </c>
-      <c r="AO15">
-        <v>-2.156657963446475</v>
-      </c>
-      <c r="AP15">
-        <v>-12.18778625954199</v>
+        <v>-3.79</v>
       </c>
       <c r="AQ15">
-        <v>-2.260536398467433</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Genesis Growth Tech Acquisition Corp. (NasdaqGM:GGAA)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K16">
-        <v>-0.398</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>1.34</v>
-      </c>
-      <c r="V16">
-        <v>0.004090354090354091</v>
-      </c>
-      <c r="W16">
-        <v>39.8</v>
-      </c>
-      <c r="X16">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y16">
-        <v>39.7275457809593</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>-6.116504854368932</v>
-      </c>
-      <c r="AB16">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC16">
-        <v>-6.188959073409637</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
-      <c r="AG16">
-        <v>-1.34</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AI16">
-        <v>-0</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.004107153803714829</v>
-      </c>
-      <c r="AK16">
-        <v>0.08792650918635171</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1.49</v>
-      </c>
-      <c r="AQ16">
-        <v>1.268456375838926</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>VT5 Acquisition Company AG (SWX:VT5)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>-0</v>
-      </c>
-      <c r="N17">
-        <v>-0</v>
-      </c>
-      <c r="P17">
-        <v>-0</v>
-      </c>
-      <c r="Q17">
-        <v>-0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>3.62</v>
-      </c>
-      <c r="V17">
-        <v>0.01635788522367827</v>
-      </c>
-      <c r="X17">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB17">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>-3.62</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>-0.01662991547225285</v>
-      </c>
-      <c r="AK17">
-        <v>1</v>
-      </c>
-      <c r="AL17">
-        <v>0.344</v>
-      </c>
-      <c r="AM17">
-        <v>0.251</v>
-      </c>
-      <c r="AO17">
-        <v>-14.15697674418605</v>
-      </c>
-      <c r="AQ17">
-        <v>-19.40239043824701</v>
+        <v>0.604221635883905</v>
       </c>
     </row>
   </sheetData>
